--- a/tools/_out/brennancad_20261021/regen/stage/tee/DesignTable_5504_SW2.xlsx
+++ b/tools/_out/brennancad_20261021/regen/stage/tee/DesignTable_5504_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM10"/>
+  <dimension ref="A1:AM12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1831,6 +1831,284 @@
       <c r="AM10" t="inlineStr">
         <is>
           <t>5504-20-20-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>5504-24-24-FG</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.92957</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.92957</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.562</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.562</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.73909</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.73909</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.47867</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>5504-24-24-FG</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>90 deg Female Pipe Elbow, 1 1/2-11 1/2 NPTF (female) x 1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>5504</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N1_1@DRIVE, N1_2@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, W@REF] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5504-24-24 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the tap drill carried to the crossing (ASSUMPTION: Air-Way publishes no bore for this part); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5504-24-24 dims are NOT assumed; confirm before modelling | Brennan CAD record 5504-24-24-FG (PARTcommunity / CADENAS, N1_1@DRIVE=N, N1_2@DRIVE=N1, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A2@DRIVE=A2THD, W@REF=Y; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL2@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>5504-24-24-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>5504-32-32-FG</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.16957</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.16957</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.812</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.812</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.81125</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.81125</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.62301</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>5504-32-32-FG</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>90 deg Female Pipe Elbow, 2-11 1/2 NPTF (female) x 2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>5504</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N1_1@DRIVE, N1_2@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, W@REF] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5504-32-32 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the tap drill carried to the crossing (ASSUMPTION: Air-Way publishes no bore for this part); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5504-32-32 dims are NOT assumed; confirm before modelling | Brennan CAD record 5504-32-32-FG (PARTcommunity / CADENAS, N1_1@DRIVE=N, N1_2@DRIVE=N1, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A2@DRIVE=A2THD, W@REF=Y; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL2@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>5504-32-32-FG</t>
         </is>
       </c>
     </row>
